--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU01/HRM/post DDV_HRM-2031-0100/Panel 7/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU01/HRM/post DDV_HRM-2031-0100/Panel 7/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Front_Summary.xlsx
@@ -532,13 +532,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.61413</v>
+        <v>16.67445</v>
       </c>
       <c r="D4" t="n">
         <v>16.17388</v>
       </c>
       <c r="E4" t="n">
-        <v>16.67445</v>
+        <v>16.61413</v>
       </c>
       <c r="F4" t="n">
         <v>54.67138</v>
@@ -563,13 +563,13 @@
         </is>
       </c>
       <c r="C5" t="n">
+        <v>16.94344</v>
+      </c>
+      <c r="D5" t="n">
         <v>16.34083</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>16.51169</v>
-      </c>
-      <c r="E5" t="n">
-        <v>16.94344</v>
       </c>
       <c r="F5" t="n">
         <v>54.25195</v>
@@ -597,10 +597,10 @@
         <v>16.96619</v>
       </c>
       <c r="D6" t="n">
+        <v>16.3447</v>
+      </c>
+      <c r="E6" t="n">
         <v>16.65788</v>
-      </c>
-      <c r="E6" t="n">
-        <v>16.3447</v>
       </c>
       <c r="F6" t="n">
         <v>56.02657</v>
@@ -628,10 +628,10 @@
         <v>17.0611</v>
       </c>
       <c r="D7" t="n">
+        <v>16.4613</v>
+      </c>
+      <c r="E7" t="n">
         <v>16.67535</v>
-      </c>
-      <c r="E7" t="n">
-        <v>16.4613</v>
       </c>
       <c r="F7" t="n">
         <v>55.72179</v>
@@ -656,13 +656,13 @@
         </is>
       </c>
       <c r="C8" t="n">
+        <v>16.57181</v>
+      </c>
+      <c r="D8" t="n">
         <v>16.31534</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>16.48102</v>
-      </c>
-      <c r="E8" t="n">
-        <v>16.57181</v>
       </c>
       <c r="F8" t="n">
         <v>54.57156</v>
@@ -690,10 +690,10 @@
         <v>16.66523</v>
       </c>
       <c r="D9" t="n">
+        <v>16.57627</v>
+      </c>
+      <c r="E9" t="n">
         <v>16.58653</v>
-      </c>
-      <c r="E9" t="n">
-        <v>16.57627</v>
       </c>
       <c r="F9" t="n">
         <v>55.53867</v>
@@ -799,10 +799,10 @@
         <v>16.71145</v>
       </c>
       <c r="D12" t="n">
+        <v>16.24094</v>
+      </c>
+      <c r="E12" t="n">
         <v>16.33146</v>
-      </c>
-      <c r="E12" t="n">
-        <v>16.24094</v>
       </c>
       <c r="F12" t="n">
         <v>55.22147</v>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="C13" t="n">
+        <v>16.93205</v>
+      </c>
+      <c r="D13" t="n">
         <v>16.5323</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>16.60764</v>
-      </c>
-      <c r="E13" t="n">
-        <v>16.93205</v>
       </c>
       <c r="F13" t="n">
         <v>55.16026</v>
@@ -889,10 +889,10 @@
         </is>
       </c>
       <c r="C15" t="n">
+        <v>16.71819</v>
+      </c>
+      <c r="D15" t="n">
         <v>16.46423</v>
-      </c>
-      <c r="D15" t="n">
-        <v>16.71819</v>
       </c>
       <c r="E15" t="n">
         <v>16.6445</v>
@@ -982,10 +982,10 @@
         </is>
       </c>
       <c r="C18" t="n">
+        <v>16.79402</v>
+      </c>
+      <c r="D18" t="n">
         <v>16.50734</v>
-      </c>
-      <c r="D18" t="n">
-        <v>16.79402</v>
       </c>
       <c r="E18" t="n">
         <v>16.75773</v>
@@ -1016,10 +1016,10 @@
         <v>16.91906</v>
       </c>
       <c r="D19" t="n">
+        <v>16.63838</v>
+      </c>
+      <c r="E19" t="n">
         <v>16.70409</v>
-      </c>
-      <c r="E19" t="n">
-        <v>16.63838</v>
       </c>
       <c r="F19" t="n">
         <v>54.50962</v>
@@ -1047,10 +1047,10 @@
         <v>16.90717</v>
       </c>
       <c r="D20" t="n">
+        <v>16.60679</v>
+      </c>
+      <c r="E20" t="n">
         <v>16.6641</v>
-      </c>
-      <c r="E20" t="n">
-        <v>16.60679</v>
       </c>
       <c r="F20" t="n">
         <v>55.01615</v>
@@ -1129,13 +1129,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>16.24367</v>
+        <v>16.50808</v>
       </c>
       <c r="D23" t="n">
         <v>16.22159</v>
       </c>
       <c r="E23" t="n">
-        <v>16.50808</v>
+        <v>16.24367</v>
       </c>
       <c r="F23" t="n">
         <v>20.87306</v>
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>16.33004</v>
+        <v>16.46691</v>
       </c>
       <c r="D26" t="n">
         <v>15.83376</v>
       </c>
       <c r="E26" t="n">
-        <v>16.46691</v>
+        <v>16.33004</v>
       </c>
       <c r="F26" t="n">
         <v>21.52598</v>
@@ -1217,13 +1217,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>16.38673</v>
+        <v>16.4859</v>
       </c>
       <c r="D27" t="n">
         <v>15.89123</v>
       </c>
       <c r="E27" t="n">
-        <v>16.4859</v>
+        <v>16.38673</v>
       </c>
       <c r="F27" t="n">
         <v>21.70606</v>
